--- a/4.evidence/ITGC/ChangeManagement_SampleSubmissionList_FY2025.xlsx
+++ b/4.evidence/ITGC/ChangeManagement_SampleSubmissionList_FY2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -143,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,7 +160,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -608,11 +611,12 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ITGC-CM-001_25件対応_RAW_*.csv / 代表3件の変更申請書PDF</t>
+          <t>ChangeManagement_Register_Detailed_FY2025.csv / 代表3件の変更申請書PDF</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -650,10 +654,10 @@
           <t>REL-2025-002</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>45859</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>45876</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -671,10 +675,10 @@
           <t>REL-2025-004</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>46016</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -692,10 +696,10 @@
           <t>REL-2025-006</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>45894</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <v>45908</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -713,10 +717,10 @@
           <t>REL-2025-008</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>45818</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="10" t="n">
         <v>45841</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -734,10 +738,10 @@
           <t>REL-2025-010</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <v>45791</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="10" t="n">
         <v>45808</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -755,10 +759,10 @@
           <t>REL-2025-012</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>45848</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>45877</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -776,10 +780,10 @@
           <t>REL-2025-014</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <v>46026</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>46046</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -797,10 +801,10 @@
           <t>REL-2025-016</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>45862</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="10" t="n">
         <v>45876</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -818,10 +822,10 @@
           <t>REL-2025-018</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <v>46096</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="10" t="n">
         <v>46106</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -839,10 +843,10 @@
           <t>REL-2025-020</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>46013</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -860,10 +864,10 @@
           <t>REL-2025-022</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <v>46067</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="10" t="n">
         <v>46091</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -881,10 +885,10 @@
           <t>REL-2025-024</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="10" t="n">
         <v>45832</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="10" t="n">
         <v>45862</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -902,10 +906,10 @@
           <t>REL-2025-026</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>46106</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="10" t="n">
         <v>46117</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -923,10 +927,10 @@
           <t>REL-2025-028</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>45753</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="10" t="n">
         <v>45773</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -944,10 +948,10 @@
           <t>REL-2025-030</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <v>45974</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="10" t="n">
         <v>46000</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -965,10 +969,10 @@
           <t>REL-2025-032</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>45788</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="10" t="n">
         <v>45811</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -986,10 +990,10 @@
           <t>REL-2025-034</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>46054</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="10" t="n">
         <v>46081</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1007,10 +1011,10 @@
           <t>REL-2025-036</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>46084</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="10" t="n">
         <v>46099</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1028,10 +1032,10 @@
           <t>REL-2025-038</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>45833</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="10" t="n">
         <v>45843</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1049,10 +1053,10 @@
           <t>REL-2025-040</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="10" t="n">
         <v>45881</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="10" t="n">
         <v>45901</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1070,10 +1074,10 @@
           <t>REL-2025-042</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="10" t="n">
         <v>45875</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="10" t="n">
         <v>45904</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1091,10 +1095,10 @@
           <t>REL-2025-044</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>45809</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="10" t="n">
         <v>45830</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1112,10 +1116,10 @@
           <t>REL-2025-046</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="10" t="n">
         <v>46089</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="10" t="n">
         <v>46111</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1133,10 +1137,10 @@
           <t>REL-2025-048</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="10" t="n">
         <v>45979</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="10" t="n">
         <v>45994</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1154,10 +1158,10 @@
           <t>REL-2025-050</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="10" t="n">
         <v>45755</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="10" t="n">
         <v>45777</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
